--- a/Payment Methods.xlsx
+++ b/Payment Methods.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29930"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\P2P\AP Payments\SOPS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhinoism\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EFC85C5-ED5B-4028-95A1-BBD4F07348FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BCDF484-415C-4FD1-91CC-DF08A85B9720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{65FFE1DC-8CB6-4AA0-A185-89F5C7A1111B}"/>
+    <workbookView xWindow="6960" yWindow="5580" windowWidth="21600" windowHeight="11385" activeTab="5" xr2:uid="{65FFE1DC-8CB6-4AA0-A185-89F5C7A1111B}"/>
   </bookViews>
   <sheets>
     <sheet name="P&amp;S" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="SEPA" sheetId="5" r:id="rId3"/>
     <sheet name="Blocks" sheetId="3" r:id="rId4"/>
     <sheet name="CC" sheetId="4" r:id="rId5"/>
+    <sheet name="PM US-CAN-MEX" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="338">
   <si>
     <t>CC</t>
   </si>
@@ -994,6 +995,69 @@
   </si>
   <si>
     <t>P&amp;S</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>HSBC to HSBC</t>
+  </si>
+  <si>
+    <t>USD Payment</t>
+  </si>
+  <si>
+    <t>Manual payment</t>
+  </si>
+  <si>
+    <t>Any other but HSBC</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>Any other but BBVA</t>
+  </si>
+  <si>
+    <t>BBA to BBVA</t>
+  </si>
+  <si>
+    <t>ACH</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>Wire</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Check</t>
+  </si>
+  <si>
+    <t>Manual Wire</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>CAD ACH Wire</t>
+  </si>
+  <si>
+    <t>EFT CAD Account</t>
+  </si>
+  <si>
+    <t>EFT USD Account</t>
+  </si>
+  <si>
+    <t>USD ACH</t>
   </si>
 </sst>
 </file>
@@ -1137,9 +1201,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1177,7 +1241,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1283,7 +1347,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1425,7 +1489,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1434,7 +1498,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D61D40B-1B77-4B7A-A633-EA9525AA1D74}">
   <dimension ref="A1:F131"/>
-  <sheetFormatPr defaultColWidth="5.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="5.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -2117,7 +2181,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="30.75">
+    <row r="81" spans="1:5" ht="30">
       <c r="B81" s="1">
         <v>6</v>
       </c>
@@ -2128,7 +2192,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="30.75">
+    <row r="82" spans="1:5" ht="30">
       <c r="B82" s="1">
         <v>7</v>
       </c>
@@ -2558,7 +2622,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A453323-74ED-4994-AD10-302736A80CCE}">
   <dimension ref="A1:F63"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -3124,7 +3188,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A3AAC05-39B1-46DA-B478-89C116711B70}">
   <dimension ref="A1:G162"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
@@ -4586,7 +4650,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3643166C-2574-4585-B804-918440FAE125}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
     <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
@@ -4664,7 +4728,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83610CDC-5730-4D13-9D8E-B4B94F418DE7}">
   <dimension ref="A1:D28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
@@ -4841,6 +4905,272 @@
     <row r="28" spans="4:4">
       <c r="D28">
         <v>2817</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6242CB75-8A17-4CF4-8D09-38ABB805392F}">
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1">
+        <v>1505</v>
+      </c>
+      <c r="B1" s="1">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="B2" s="1">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="B3" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="B4" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C4" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>1552</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="B7" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="B8" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C8" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>1095</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C9" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="B10" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C10" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="B11" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C11" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="B12" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C12" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>1729</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C13" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="B14" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C14" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="B15" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C15" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="B16" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C16" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
+        <v>1265</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C17" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="B18" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C18" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="B19" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C19" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="B20" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C20" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>1129</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C21" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="B22" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C22" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="B23" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C23" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="B24" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C24" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
+        <v>1513</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C25" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="B26" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C26" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="B27" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C27" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="B28" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C28" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="B29" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C29" t="s">
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -4849,6 +5179,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="bc1a8bde-03fe-420e-98f1-339f16543cfb" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e9aecb19-12ff-4b0a-a9fa-52e9852c3955">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C8042D9A2E3BF943A3C8E37CE2A4636D" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="985293529ec67e58e4aaf8c79fba31ba">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e9aecb19-12ff-4b0a-a9fa-52e9852c3955" xmlns:ns3="bc1a8bde-03fe-420e-98f1-339f16543cfb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5912a47d6406023d5fd6fd10bf0b2397" ns2:_="" ns3:_="">
     <xsd:import namespace="e9aecb19-12ff-4b0a-a9fa-52e9852c3955"/>
@@ -5083,17 +5424,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="bc1a8bde-03fe-420e-98f1-339f16543cfb" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e9aecb19-12ff-4b0a-a9fa-52e9852c3955">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -5104,13 +5434,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DFB199C-59A8-4F13-B8C5-EFDA7C18FF7E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6930C10-1CCA-4D4F-B61A-C71F2326A091}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="bc1a8bde-03fe-420e-98f1-339f16543cfb"/>
+    <ds:schemaRef ds:uri="e9aecb19-12ff-4b0a-a9fa-52e9852c3955"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6930C10-1CCA-4D4F-B61A-C71F2326A091}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DFB199C-59A8-4F13-B8C5-EFDA7C18FF7E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="e9aecb19-12ff-4b0a-a9fa-52e9852c3955"/>
+    <ds:schemaRef ds:uri="bc1a8bde-03fe-420e-98f1-339f16543cfb"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B14A0C-69B2-4515-921E-D29B0D99FC4F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B14A0C-69B2-4515-921E-D29B0D99FC4F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>